--- a/vkr/VKR_findata.xlsx
+++ b/vkr/VKR_findata.xlsx
@@ -11,9 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Данные_Юрент" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Затраты" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Эффекты" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводная_финмодель" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Чувствительность" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="УПС_расчёт" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="УПС_расчёт" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводная_финмодель" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Чувствительность" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,12 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="+0.0;-0.0;0.0"/>
-    <numFmt numFmtId="166" formatCode="+#,##0.0;-#,##0.0;0.0"/>
+    <numFmt numFmtId="166" formatCode="0&quot; %&quot;"/>
+    <numFmt numFmtId="167" formatCode="+#,##0.0;-#,##0.0;0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,11 +66,6 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -95,16 +91,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -170,11 +166,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,11 +184,15 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -200,26 +201,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -585,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -604,7 +607,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Автор: [ФИО студента], ВКР НИУ ВШЭ, 2026</t>
+          <t>Автор: [ФИО студента], ВКР НИУ ВШЭ, 2026 г.</t>
         </is>
       </c>
     </row>
@@ -614,28 +617,28 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Назначение файла. Этот Excel содержит расчётную часть финансовой модели сценария S3</t>
+          <t>Назначение файла. Расчётная часть финансовой модели сценария S3 (диверсификация</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>(диверсификация режимов конкурентных действий МТС Юрент по портфелю региональных</t>
+          <t>режимов конкурентных действий МТС Юрент по портфелю региональных рынков</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>рынков кикшеринга) на горизонте 12 месяцев. Все цифры из §3.4 ВКР воспроизводимы</t>
+          <t>кикшеринга) на горизонте 12 и 24 месяцев. Все цифры из §3.4 ВКР воспроизводимы</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>непосредственно из ячеек этого файла; формулы открыты.</t>
+          <t>из ячеек этого файла; формулы открыты, циклических ссылок нет.</t>
         </is>
       </c>
     </row>
@@ -652,139 +655,205 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Данные_Юрент — сырые данные эксперта А. по 5 городам портфеля (поквартально,</t>
+          <t xml:space="preserve">  • README — описание модели и источников.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2024 и 9 месяцев 2025): выручка, парк, активные пользователи, поездки.</t>
+          <t xml:space="preserve">  • Данные_Юрент — сырые данные эксперта А. по 5 городам портфеля</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Затраты — статьи затрат на реализацию S3 (региональное управление, маркетинг,</t>
+          <t xml:space="preserve">    (поквартально, 2024 и 9 месяцев 2025): выручка, парк, активные пользователи,</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    инфраструктура и пилот УПС, накладные).</t>
+          <t xml:space="preserve">    поездки. На основе этих данных рассчитываются производные показатели</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Эффекты — статьи эффектов с допущениями и формулами по 4 источникам:</t>
+          <t xml:space="preserve">    (выручка итого, утилизация, средний чек, YoY).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    рост R2, УПС-пилот, оптимизация R3, экономия R1.</t>
+          <t xml:space="preserve">  • Затраты — статьи затрат на реализацию S3: региональное управление (A),</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Сводная_финмодель — затраты, эффекты, чистый эффект S3 vs S1 (год 1).</t>
+          <t xml:space="preserve">    маркетинг (B), инфраструктура и пилот УПС (C), накладные (D).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Чувствительность — три сценария (консервативный, базовый, оптимистичный).</t>
+          <t xml:space="preserve">  • Эффекты — статьи эффектов с допущениями: R2 рост, УПС-пилот, R3 Москва,</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • УПС_расчёт — детальная разбивка по проектному инструменту (пилот в Екатеринбурге).</t>
+          <t xml:space="preserve">    R1 малые города.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Сводная_финмодель — затраты, эффекты, чистый эффект S3 vs S1 (год 1 + год 2).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Источники данных:</t>
+          <t xml:space="preserve">  • Чувствительность — сценарии (консервативный, базовый, оптимистичный)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Внутренняя поквартальная отчётность МТС Юрент по 86 субъектам РФ</t>
+          <t xml:space="preserve">    с пересчётом результата по 4 ключевым параметрам.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    за 2024 и 9 месяцев 2025 (данные эксперта А., руководитель M&amp;A ПАО «МТС»).</t>
+          <t xml:space="preserve">  • УПС_расчёт — детальная разбивка пилота в Екатеринбурге (как в §3.2 ВКР).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Публичная отчётность ПАО «ВУШ Холдинг» по МСФО (9 мес. 2024) — для калибровки</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    OpEx/Выручка и EBITDA-маржи бенчмарк-оператора.</t>
+          <t>Источники данных:</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Расчёт по проектному инструменту УПС (§3.2 ВКР).</t>
+          <t xml:space="preserve">  • Внутренняя поквартальная отчётность МТС Юрент по 86 субъектам РФ за 2024 г.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    и 9 месяцев 2025 г. (эксперт А., руководитель подразделения M&amp;A ПАО «МТС»).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Все статьи с допущениями явно маркированы [ДОПУЩЕНИЕ] в столбце «Источник / допущение».</t>
+          <t xml:space="preserve">  • Публичная отчётность ПАО «ВУШ Холдинг» по МСФО (9 мес. 2024) — для калибровки</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Точная калибровка модели возможна после получения внутренних данных МТС Юрент по</t>
+          <t xml:space="preserve">    OpEx/Выручка и EBITDA-маржи бенчмарк-оператора.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>операционным издержкам и поведению пользователей; в текущей конфигурации модель</t>
+          <t xml:space="preserve">  • Расчёт по проектному инструменту УПС (§3.2 ВКР).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>обеспечивает оценку порядка величин и направления эффекта.</t>
+      <c r="A31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Допущения, требующие калибровки на этапе пилота:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — прирост темпа выручки R2-городов от дифференциации: 1–5 п.п. (база 3 п.п.);</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — доля замещения физической ребалансировки стимулами: 10–30 % (база 20 %);</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — стоимость физической ребалансировки: 120 руб./операция (отраслевая оценка);</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — доля ребалансировки в OpEx: ≈30 % (по аналогии с международными данными);</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — снижение OpEx Москвы в режиме R3: 1–3 % от выручки (база 2 %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Все статьи с допущениями явно маркированы [ДОПУЩЕНИЕ] в столбце «Источник».</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Точная калибровка модели возможна после доступа к внутренним данным</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>МТС Юрент по операционным издержкам и поведению пользователей на пилоте.</t>
         </is>
       </c>
     </row>
@@ -802,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -834,7 +903,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Город</t>
@@ -847,17 +916,17 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Q2 2024 выручка, руб.</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Q3 2024 выручка, руб.</t>
+          <t>Q3 2024</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Q4 2024 выручка, руб.</t>
+          <t>Q4 2024</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -867,17 +936,17 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Q1 2025 выручка, руб.</t>
+          <t>Q1 2025</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Q2 2025 выручка, руб.</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Q3 2025 выручка, руб.</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -887,12 +956,12 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Парк на 30.09.2024, шт.</t>
+          <t>Парк 30.09.2024</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>Парк на 30.09.2025, шт.</t>
+          <t>Парк 30.09.2025</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
@@ -997,8 +1066,9 @@
         <f>M3/K3</f>
         <v/>
       </c>
-      <c r="S3" s="10" t="n">
-        <v>-7.906049694046313</v>
+      <c r="S3" s="10">
+        <f>(J3/SUM(B3:D3)-1)*100</f>
+        <v/>
       </c>
       <c r="T3" s="10" t="n">
         <v>-6.638959885165018</v>
@@ -1065,8 +1135,9 @@
         <f>M4/K4</f>
         <v/>
       </c>
-      <c r="S4" s="10" t="n">
-        <v>41.0555011305648</v>
+      <c r="S4" s="10">
+        <f>(J4/SUM(B4:D4)-1)*100</f>
+        <v/>
       </c>
       <c r="T4" s="10" t="n">
         <v>42.31219715991428</v>
@@ -1133,8 +1204,9 @@
         <f>M5/K5</f>
         <v/>
       </c>
-      <c r="S5" s="10" t="n">
-        <v>-5.596479278372724</v>
+      <c r="S5" s="10">
+        <f>(J5/SUM(B5:D5)-1)*100</f>
+        <v/>
       </c>
       <c r="T5" s="10" t="n">
         <v>-10.23043686569426</v>
@@ -1201,8 +1273,9 @@
         <f>M6/K6</f>
         <v/>
       </c>
-      <c r="S6" s="10" t="n">
-        <v>-4.319000282014763</v>
+      <c r="S6" s="10">
+        <f>(J6/SUM(B6:D6)-1)*100</f>
+        <v/>
       </c>
       <c r="T6" s="10" t="n">
         <v>4.149916068372117</v>
@@ -1269,8 +1342,9 @@
         <f>M7/K7</f>
         <v/>
       </c>
-      <c r="S7" s="10" t="n">
-        <v>143.2245776240149</v>
+      <c r="S7" s="10">
+        <f>(J7/SUM(B7:D7)-1)*100</f>
+        <v/>
       </c>
       <c r="T7" s="10" t="n">
         <v>128.9371003780587</v>
@@ -1294,28 +1368,55 @@
         <f>SUM(K3:K7)</f>
         <v/>
       </c>
+      <c r="L8" s="7">
+        <f>SUM(L3:L7)</f>
+        <v/>
+      </c>
       <c r="M8" s="7">
         <f>SUM(M3:M7)</f>
         <v/>
       </c>
+      <c r="N8" s="7">
+        <f>SUM(N3:N7)</f>
+        <v/>
+      </c>
+      <c r="O8" s="7">
+        <f>SUM(O3:O7)</f>
+        <v/>
+      </c>
+      <c r="P8" s="7">
+        <f>SUM(P3:P7)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="12">
+        <f>F8/M8</f>
+        <v/>
+      </c>
+      <c r="R8" s="13">
+        <f>M8/K8</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Источник: внутренняя поквартальная отчётность МТС Юрент по регионам РФ (эксперт А., данные на 30.09.2025).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Выручка — без НДС, включая партнёров и франчайзи на территории РФ.</t>
-        </is>
-      </c>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Источник: внутренняя поквартальная отчётность МТС Юрент по регионам РФ (эксперт А., данные на 30.09.2025). Выручка — без НДС, включая партнёров и франчайзи на территории РФ.</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="16" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A10:J10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1333,7 +1434,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1345,44 +1446,44 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Блок</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Расчёт</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Сумма, тыс. руб./год</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Источник / допущение</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>A. Региональное управление</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>3 региональных менеджера</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>3 региональных менеджера по кластерам режимов</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>3 × 350 × 12</t>
         </is>
@@ -1390,24 +1491,24 @@
       <c r="D3" s="6" t="n">
         <v>12600</v>
       </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>ФОТ gross 350 тыс. руб./мес. с налогами и соцпакетом [ДОПУЩЕНИЕ — рыночная вилка для уровня middle management в МТС]</t>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>ФОТ gross 350 тыс. руб./мес. с налогами и соцпакетом [ДОПУЩЕНИЕ — рыночная вилка middle management в МТС]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>A. Региональное управление</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>3 региональных аналитика</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>3 × 200 × 12</t>
         </is>
@@ -1415,49 +1516,49 @@
       <c r="D4" s="6" t="n">
         <v>7200</v>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>ФОТ gross 200 тыс. руб./мес. [ДОПУЩЕНИЕ — стандартная вилка для аналитиков]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>A. Региональное управление</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Накладные (командировки, BI-инструменты, рабочие места)</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>~10% от ФОТ</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>[ДОПУЩЕНИЕ — стандартный коэффициент 10 % к ФОТ]</t>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>[ДОПУЩЕНИЕ]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>B. Маркетинг S3</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Исследования и креатив для трёх режимных кампаний</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1465,24 +1566,24 @@
       <c r="D6" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>[ДОПУЩЕНИЕ — без учёта медиа-инвестиций, которые финансируются из стандартного бюджета]</t>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>[ДОПУЩЕНИЕ — без учёта медиа-инвестиций из стандартного бюджета]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>B. Маркетинг S3</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>A/B-тестирование, аналитика результатов</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1490,24 +1591,24 @@
       <c r="D7" s="6" t="n">
         <v>4000</v>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>[ДОПУЩЕНИЕ]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>C. УПС-инфраструктура и пилот</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>IT-доработки (геозоны, push-таргетинг, движок стимулов, ЛК исполнителя)</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>capex однократно</t>
         </is>
@@ -1515,24 +1616,24 @@
       <c r="D8" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>[ДОПУЩЕНИЕ — оценка по аналогии с продуктовыми спринтами]</t>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>[ДОПУЩЕНИЕ — оценка по аналогии с продуктовыми спринтами Юрент]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>C. УПС-инфраструктура и пилот</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Команда пилота: 1 продакт + 1 аналитик × 6 мес.</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>2 × 400 × 6</t>
         </is>
@@ -1540,70 +1641,74 @@
       <c r="D9" s="6" t="n">
         <v>4800</v>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>ФОТ gross 400 тыс. руб./мес. [ДОПУЩЕНИЕ]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>C. УПС-инфраструктура и пилот</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Бюджет стимулов и микрозаданий (Екб, сезон)</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Бюджет стимулов и микрозаданий в Екатеринбурге за сезон</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>базовый сценарий §3.2</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2820</v>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Расчёт §3.2 ВКР (4,6× ниже стоимости физ. ребалансировки 120 руб./опер.)</t>
+        <v>1000</v>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Расчёт §3.2 ВКР: 26,5 руб./опер × ≈ 37 500 замещ. операций (см. лист «УПС_расчёт»)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>C. УПС-инфраструктура и пилот</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Резерв и непредвиденные</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Резерв на масштабирование стимульной кампании и непредвиденные</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>380</v>
-      </c>
-      <c r="E11" s="14" t="inlineStr"/>
+        <v>2200</v>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>[ДОПУЩЕНИЕ — для сценариев A/B/C доля стимулов меняется в 2–3 раза]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>D. Накладные и обучение</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Обучение региональных менеджеров и аналитиков</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1611,24 +1716,24 @@
       <c r="D12" s="6" t="n">
         <v>1500</v>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>[ДОПУЩЕНИЕ]</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>D. Накладные и обучение</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Управленческий резерв</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1636,7 +1741,7 @@
       <c r="D13" s="6" t="n">
         <v>1500</v>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>[ДОПУЩЕНИЕ]</t>
         </is>
@@ -1645,7 +1750,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>ИТОГО затраты S3, год 1</t>
+          <t>ИТОГО затраты S3, год 1, тыс. руб.</t>
         </is>
       </c>
       <c r="D14" s="7">
@@ -1670,12 +1775,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1685,155 +1790,156 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+    <row r="2" ht="35" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Эффект</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Город / кластер</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>База расчёта</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Параметр / допущение</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>EBITDA-эффект, тыс. руб.</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>EBITDA-эффект, тыс. руб./год</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Эффект 1. R2 атака: прирост выручки</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>СПб + Екб + Крд + Нск</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Выручка 2024 R2-портфеля: 1,544 млн руб.</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>+3 п.п. к темпу выручки YoY (диапазон 1–5 п.п.) × EBITDA-маржа 25 %</t>
-        </is>
-      </c>
-      <c r="E3" s="16">
-        <f>1544195*0.03*0.25</f>
-        <v/>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>§3.4 ВКР; [ДОПУЩЕНИЕ] о приросте темпа</t>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Выручка 2024 R2-портфеля: 1,544.2 млн руб.</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>+3 п.п. к темпу выручки YoY (база; диапазон 1–5 п.п.) × EBITDA-маржа 25 %</t>
+        </is>
+      </c>
+      <c r="E3" s="20">
+        <f>ROUND(1544194.813*0.03*0.25,0)</f>
+        <v/>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>§3.4 ВКР</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Эффект 2. УПС-пилот Екатеринбург</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Екатеринбург</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Парк 6448, утилизация 319, средний чек 75 руб.</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Замещение 20 % ребалансировки стимулами (базовый сценарий §3.2)</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>9790</v>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>§3.2 ВКР: 4,48 млн экономии + 8,14 млн доп. выручки – 2,82 млн стимулы</t>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Базовый сценарий (замещение 20 % ребалансировки) — см. лист УПС_расчёт</t>
+        </is>
+      </c>
+      <c r="E4" s="20">
+        <f>'УПС_расчёт'!$C$26</f>
+        <v/>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>§3.2 ВКР, лист «УПС_расчёт»</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Эффект 3. R3 Москва: оптимизация OpEx</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Выручка 2024 Москвы: 2,626 млн руб.</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Снижение OpEx на 2 % от выручки рынка (диапазон 1–3 %)</t>
-        </is>
-      </c>
-      <c r="E5" s="16">
-        <f>2626407*0.02</f>
-        <v/>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>§3.4 ВКР; [ДОПУЩЕНИЕ] о глубине оптимизации</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Выручка 2024 Москвы: 2,626.4 млн руб.</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>2 % от выручки рынка (база; диапазон 1–3 %)</t>
+        </is>
+      </c>
+      <c r="E5" s="20">
+        <f>ROUND(2626406.974*0.02,0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>§3.4 ВКР; [ДОПУЩЕНИЕ]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Эффект 4. R1 малые города: экономия капвложений</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Малые города</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>За пределами портфеля 5 городов</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>~10 млн руб. экономии капвложений (диапазон 5–20)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>~10 млн руб. экономии капвложений (диапазон 5–20); эффект на EBITDA ≈ 30 %</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>§3.4 ВКР; [ДОПУЩЕНИЕ]</t>
         </is>
@@ -1842,7 +1948,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>ИТОГО эффект S3, год 1</t>
+          <t>ИТОГО эффект S3, год 1, тыс. руб.</t>
         </is>
       </c>
       <c r="E7" s="7">
@@ -1864,239 +1970,536 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Сводная финансовая модель S3 (год 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>Млн руб.</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>Источник</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Детальный расчёт пилота УПС в Екатеринбурге (соответствует §3.2 ВКР)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Источник / расчёт</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Затраты, всего</t>
-        </is>
-      </c>
-      <c r="B3" s="18">
-        <f>-Затраты!D14/1000</f>
-        <v/>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>Лист «Затраты», итого</t>
+      <c r="A3" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Парк Екб на 30.09.2024, шт.</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>6448</v>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>данные эксперта А.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 1. R2-прирост выручки (СПб, Екб, Крд, Нск)</t>
-        </is>
-      </c>
-      <c r="B4" s="20">
-        <f>Эффекты!E3/1000</f>
-        <v/>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>+3 п.п. × выручка R2 × EBITDA 25 %</t>
+      <c r="A4" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Поездки Екб за сезон Q2+Q3 2024, шт.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1819014</v>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>данные эксперта А. (Q2 565 936 + Q3 1 253 078)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 2. УПС-пилот Екатеринбург</t>
-        </is>
-      </c>
-      <c r="B5" s="20">
-        <f>Эффекты!E4/1000</f>
-        <v/>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>§3.2, базовый сценарий</t>
+      <c r="A5" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Средний чек Екб 2024, руб.</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>выручка/поездки 2024 ≈ 74,6 руб. (данные эксперта А.)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 3. R3 Москва: оптимизация OpEx</t>
-        </is>
-      </c>
-      <c r="B6" s="20">
-        <f>Эффекты!E5/1000</f>
-        <v/>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>2 % выручки Москвы</t>
+      <c r="A6" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Утилизация 2024, поездок/самокат/год</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>319</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>поездки 2024 / парк (данные эксперта А.)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 4. R1 малые города: экономия капвложений</t>
-        </is>
-      </c>
-      <c r="B7" s="20">
-        <f>Эффекты!E6/1000</f>
-        <v/>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>Защита от нерентабельных инвестиций</t>
+      <c r="A7" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>OpEx / Выручка, %</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Whoosh 48 % (МСФО, 9 мес. 2024) + 7 п.п. поправка на масштаб</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Эффект, всего</t>
-        </is>
-      </c>
-      <c r="B8" s="21">
-        <f>SUM(B4:B7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>ЧИСТЫЙ ЭФФЕКТ S3 vs S1, год 1</t>
-        </is>
-      </c>
-      <c r="B9" s="23">
-        <f>B3+SUM(B4:B7)</f>
-        <v/>
+      <c r="A8" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Доля ребалансировки в OpEx, %</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>[ДОПУЩЕНИЕ — по аналогии с международными исследованиями]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Стоимость физической ребалансировки, руб./операция</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>[ДОПУЩЕНИЕ — отраслевая оценка; подлежит калибровке]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Стимул на стороне точки высадки, руб.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>[ДОПУЩЕНИЕ; доля случаев 50 %]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Стимул на стороне точки посадки, руб.</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>[ДОПУЩЕНИЕ; доля случаев 30 %]</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>Прогноз год 2 (тиражирование УПС на СПб, Крд, Нск)</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="26" t="n"/>
+      <c r="A12" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Стимул внешнему исполнителю, руб.</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>[ДОПУЩЕНИЕ; доля случаев 20 %]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Затраты год 2 (без capex УПС, +0 capex)</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="n">
-        <v>-37</v>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>A + B + D + операционная часть C</t>
+      <c r="A13" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Средневзвешенная стоимость стимула, руб./операция</t>
+        </is>
+      </c>
+      <c r="C13" s="7">
+        <f>$B$10*0.5+$B$11*0.3+$B$12*0.2</f>
+        <v/>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>B8 × 0,5 + B9 × 0,3 + B10 × 0,2</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 1 расширенный (R2-темпы +5 п.п.)</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>5 п.п. × выручка R2-портфеля × 25 %</t>
+      <c r="A14" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Замещение ребалансировки стимулами, % (базовый сценарий B)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>§3.2: A=10 %, B=20 %, C=30 %</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 2 расширенный (УПС в 4 городах R2)</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>Тиражирование §3.2 на СПб, Крд, Нск ≈ 5× базы пилота</t>
+      <c r="A15" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Прирост восстановленных поездок в пилотных зонах, %</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>[ДОПУЩЕНИЕ — доля чувствительных микролокаций]</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 3 (R3 Москва, год 2)</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="n">
-        <v>55</v>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>Углубление оптимизации до 2,1 % от выручки</t>
-        </is>
-      </c>
+      <c r="A16" s="21" t="inlineStr"/>
+      <c r="B16" s="21" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr"/>
+      <c r="D16" s="21" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 4 (R1 малые города)</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>Расширение применения каркаса</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>ЧИСТЫЙ ЭФФЕКТ S3 vs S1, год 2</t>
-        </is>
-      </c>
-      <c r="B18" s="23">
-        <f>SUM(B13:B17)</f>
+      <c r="A17" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Выручка Екб за сезон Q2+Q3, тыс. руб.</t>
+        </is>
+      </c>
+      <c r="C17" s="7">
+        <f>ROUND($B$4*$B$5/1000,0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>B2 × B3 / 1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>OpEx сезона, тыс. руб.</t>
+        </is>
+      </c>
+      <c r="C18" s="7">
+        <f>ROUND($B$17*$B$7/100,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>B14 × B5 / 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Расходы на физ. ребалансировку (сезон), тыс. руб.</t>
+        </is>
+      </c>
+      <c r="C19" s="7">
+        <f>ROUND($B$18*$B$8/100,0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>B15 × B6 / 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Базовое число операций физ. ребалансировки за сезон</t>
+        </is>
+      </c>
+      <c r="C20" s="7">
+        <f>ROUND($B$19*1000/$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>B16 × 1000 / B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Число замещённых операций (базовый B)</t>
+        </is>
+      </c>
+      <c r="C21" s="7">
+        <f>ROUND($B$20*$B$14/100,0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>B17 × B12 / 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr"/>
+      <c r="B22" s="21" t="inlineStr"/>
+      <c r="C22" s="21" t="inlineStr"/>
+      <c r="D22" s="21" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Чистая экономия от замещения, тыс. руб.</t>
+        </is>
+      </c>
+      <c r="C23" s="7">
+        <f>ROUND(($B$9-$B$13)*$B$21/1000,0)</f>
+        <v/>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>(B7 – B11) × B18 / 1000  ← платим стимул вместо физ. ребалансировки</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Дополнительная выручка от восстановленных поездок, тыс. руб.</t>
+        </is>
+      </c>
+      <c r="C24" s="7">
+        <f>ROUND($B$4*$B$15/100*$B$5/1000,0)</f>
+        <v/>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>B2 × B13 / 100 × B3 / 1000  ← устранение разрывов покрытия</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr"/>
+      <c r="B25" s="21" t="inlineStr"/>
+      <c r="C25" s="21" t="inlineStr"/>
+      <c r="D25" s="21" t="inlineStr"/>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>ЧИСТЫЙ ЭФФЕКТ УПС (базовый сценарий B), тыс. руб.</t>
+        </is>
+      </c>
+      <c r="C26" s="23">
+        <f>$B$23+$B$24</f>
+        <v/>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>B19 + B20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Сценарии чувствительности УПС (по доле замещения ребалансировки)</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>Замещение, %</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>Прирост поездок (масштаб), %</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>Чистый эффект, тыс. руб.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>A. Консервативный</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="20">
+        <f>ROUND(($B$9-$B$13)*$B$20*10/100/1000 + $B$4*3/100*$B$5/1000, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>B. Базовый</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="C31" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="20">
+        <f>ROUND(($B$9-$B$13)*$B$20*20/100/1000 + $B$4*6/100*$B$5/1000, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>C. Оптимистичный</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" s="20">
+        <f>ROUND(($B$9-$B$13)*$B$20*30/100/1000 + $B$4*9/100*$B$5/1000, 0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2108,248 +2511,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Сценарии чувствительности чистого эффекта S3 (год 1)</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Сводная финансовая модель S3</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Параметр</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>Консервативный</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>Базовый</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>Оптимистичный</t>
-        </is>
-      </c>
-      <c r="E2" s="17" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Статья</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>Млн руб.</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>Источник</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Прирост темпа R2 выручки, п.п.</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="13" t="n">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>ГОД 1 (12 месяцев)</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="16" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Затраты, всего</t>
+        </is>
+      </c>
+      <c r="B4" s="29">
+        <f>-'Затраты'!$D$14/1000</f>
+        <v/>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Лист «Затраты», итого</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 1. R2-прирост выручки (СПб, Екб, Крд, Нск)</t>
+        </is>
+      </c>
+      <c r="B5" s="30">
+        <f>'Эффекты'!$E$3/1000</f>
+        <v/>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>+3 п.п. × выручка R2 × EBITDA 25 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 2. УПС-пилот Екатеринбург</t>
+        </is>
+      </c>
+      <c r="B6" s="30">
+        <f>'Эффекты'!$E$4/1000</f>
+        <v/>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>§3.2, базовый сценарий B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 3. R3 Москва: оптимизация OpEx</t>
+        </is>
+      </c>
+      <c r="B7" s="30">
+        <f>'Эффекты'!$E$5/1000</f>
+        <v/>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>2 % выручки Москвы</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 4. R1 малые города: экономия капвложений</t>
+        </is>
+      </c>
+      <c r="B8" s="30">
+        <f>'Эффекты'!$E$6/1000</f>
+        <v/>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Защита от нерентабельных инвестиций</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Эффект, всего</t>
+        </is>
+      </c>
+      <c r="B9" s="31">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>ЧИСТЫЙ ЭФФЕКТ S3 vs S1, год 1</t>
+        </is>
+      </c>
+      <c r="B10" s="33">
+        <f>B4+SUM(B5:B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>ГОД 2 (тиражирование УПС на 3 города R2-кластера, capex выпадает)</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Затраты год 2 (без capex УПС)</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="n">
+        <v>-37</v>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>A + B + D + операционная часть C</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 1 расширенный (R2-темпы +5 п.п.)</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>+5 п.п. × выручка R2 × EBITDA 25 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 2 расширенный (УПС в 4 городах R2)</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Тиражирование §3.2 на СПб, Крд, Нск (≈ 4× базы пилота, с учётом разных утилизаций)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 3 (R3 Москва, год 2)</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>55</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Углубление оптимизации до 2,1 % от выручки</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 4 (R1 малые города)</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>Допущение о силе эффекта дифференциации</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Замещение ребалансировки УПС, %</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>Сценарии A/B/C из §3.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Оптимизация OpEx Москвы, %</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>Глубина рычагов R3 в Москве</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Экономия капвложений малые города, млн руб./год</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>Темпы расширения портфеля</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 1 (R2 темпы)</t>
-        </is>
-      </c>
-      <c r="B8" s="10">
-        <f>ROUND(1544.194813*B3/100*0.25,1)</f>
-        <v/>
-      </c>
-      <c r="C8" s="27">
-        <f>ROUND(1544.194813*C3/100*0.25,1)</f>
-        <v/>
-      </c>
-      <c r="D8" s="10">
-        <f>ROUND(1544.194813*D3/100*0.25,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 2 (УПС-пилот Екб)</t>
-        </is>
-      </c>
-      <c r="B9" s="10">
-        <f>ROUND(B4/20*9.79,1)</f>
-        <v/>
-      </c>
-      <c r="C9" s="27">
-        <f>ROUND(C4/20*9.79,1)</f>
-        <v/>
-      </c>
-      <c r="D9" s="10">
-        <f>ROUND(D4/20*9.79,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 3 (R3 Москва оптимизация)</t>
-        </is>
-      </c>
-      <c r="B10" s="10">
-        <f>ROUND(2626.406974*B5/100,1)</f>
-        <v/>
-      </c>
-      <c r="C10" s="27">
-        <f>ROUND(2626.406974*C5/100,1)</f>
-        <v/>
-      </c>
-      <c r="D10" s="10">
-        <f>ROUND(2626.406974*D5/100,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Эффект 4 (R1 малые города)</t>
-        </is>
-      </c>
-      <c r="B11" s="10">
-        <f>ROUND(B6*0.3,1)</f>
-        <v/>
-      </c>
-      <c r="C11" s="27">
-        <f>ROUND(C6*0.3,1)</f>
-        <v/>
-      </c>
-      <c r="D11" s="10">
-        <f>ROUND(D6*0.3,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Затраты S3</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>-48</v>
-      </c>
-      <c r="C12" s="28" t="n">
-        <v>-48</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>-48</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>ЧИСТЫЙ ЭФФЕКТ S3, год 1, млн руб.</t>
-        </is>
-      </c>
-      <c r="B13" s="30">
-        <f>SUM(B8:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="30">
-        <f>SUM(C8:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="30">
-        <f>SUM(D8:D12)</f>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Расширение применения каркаса</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>ЧИСТЫЙ ЭФФЕКТ S3 vs S1, год 2</t>
+        </is>
+      </c>
+      <c r="B19" s="33">
+        <f>SUM(B14:B18)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2361,350 +2765,259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Детальный расчёт пилота УПС в Екатеринбурге (§3.2 ВКР)</t>
+          <t>Сценарии чувствительности чистого эффекта S3 (год 1)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Параметр</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>Источник / расчёт</t>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>Консервативный</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>Базовый</t>
+        </is>
+      </c>
+      <c r="D2" s="27" t="inlineStr">
+        <is>
+          <t>Оптимистичный</t>
+        </is>
+      </c>
+      <c r="E2" s="27" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Парк Екб 2024 (на 30.09)</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>6448</v>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>эксперт А.</t>
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Прирост темпа R2 выручки, п.п.</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Допущение о силе эффекта дифференциации</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Поездки Екб за сезон Q2+Q3 2024, шт.</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1819014</v>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>эксперт А. (Q2 565936 + Q3 1253078)</t>
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Замещение ребалансировки УПС, %</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Сценарии A/B/C из §3.2 / лист «УПС_расчёт»</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Средний чек Екб 2024, руб.</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>выручка/поездки 2024 ≈ 74,6 руб.</t>
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Оптимизация OpEx Москвы, %</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Глубина рычагов R3 в Москве</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Утилизация 2024, поездок/самокат/год</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>319</v>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>поездки/парк</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>OpEx/Выручка для оператора-преследователя, %</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>Whoosh 48 % + 7 п.п. поправка на масштаб</t>
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Экономия капвложений в малых городах, млн руб./год</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Темпы расширения портфеля</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Доля ребалансировки в OpEx, %</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>[ДОПУЩЕНИЕ] аналогично исследованиям микромобильности</t>
-        </is>
-      </c>
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Производные эффекты</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr"/>
+      <c r="C8" s="35" t="inlineStr"/>
+      <c r="D8" s="35" t="inlineStr"/>
+      <c r="E8" s="35" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Стоимость физ. ребалансировки, руб./опер.</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>[ДОПУЩЕНИЕ — отраслевая оценка, требует калибровки]</t>
-        </is>
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 1 (R2 темпы), млн руб.</t>
+        </is>
+      </c>
+      <c r="B9" s="36">
+        <f>ROUND(1544.194813*B3/100*0.25,1)</f>
+        <v/>
+      </c>
+      <c r="C9" s="37">
+        <f>ROUND(1544.194813*C3/100*0.25,1)</f>
+        <v/>
+      </c>
+      <c r="D9" s="36">
+        <f>ROUND(1544.194813*D3/100*0.25,1)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Базовое число операций ребалансировки за сезон</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <f>B4/24</f>
-        <v/>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>≈ 1 операция на 24 поездки [допущение]</t>
-        </is>
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 2 (УПС-пилот), млн руб.</t>
+        </is>
+      </c>
+      <c r="B10" s="36">
+        <f>ROUND(B4/20*9.79,1)</f>
+        <v/>
+      </c>
+      <c r="C10" s="37">
+        <f>ROUND(C4/20*9.79,1)</f>
+        <v/>
+      </c>
+      <c r="D10" s="36">
+        <f>ROUND(D4/20*9.79,1)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Замещение ребалансировки стимулами, % (база)</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>Базовый сценарий</t>
-        </is>
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 3 (R3 Москва), млн руб.</t>
+        </is>
+      </c>
+      <c r="B11" s="36">
+        <f>ROUND(2626.406974*B5/100,1)</f>
+        <v/>
+      </c>
+      <c r="C11" s="37">
+        <f>ROUND(2626.406974*C5/100,1)</f>
+        <v/>
+      </c>
+      <c r="D11" s="36">
+        <f>ROUND(2626.406974*D5/100,1)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Число замещённых операций</t>
-        </is>
-      </c>
-      <c r="B12" s="6">
-        <f>B11*B12/100</f>
-        <v/>
-      </c>
-      <c r="C12" s="19" t="inlineStr"/>
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Эффект 4 (R1 капвложения), млн руб.</t>
+        </is>
+      </c>
+      <c r="B12" s="36">
+        <f>ROUND(B6*0.3,1)</f>
+        <v/>
+      </c>
+      <c r="C12" s="37">
+        <f>ROUND(C6*0.3,1)</f>
+        <v/>
+      </c>
+      <c r="D12" s="36">
+        <f>ROUND(D6*0.3,1)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Стоимость стимула-высадка, руб.</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>50 % случаев</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Стоимость стимула-посадка, руб.</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>30 % случаев</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Стоимость внешнего исполнителя, руб.</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>20 % случаев (дальние перемещения)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Средневзвешенная стоимость стимула, руб./опер.</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
-        <f>B14*0.5+B15*0.3+B16*0.2</f>
-        <v/>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>Сумма с весами</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Соотношение «ребалансировка/стимул»</t>
-        </is>
-      </c>
-      <c r="B17" s="6">
-        <f>B10/B17</f>
-        <v/>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>Множитель эффективности замещения</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
-      <c r="B18" s="6" t="inlineStr"/>
-      <c r="C18" s="19" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Экономия на замещении ребалансировки, тыс. руб.</t>
-        </is>
-      </c>
-      <c r="B19" s="6">
-        <f>ROUND((B13*B10-B13*B17)/1000,0)</f>
-        <v/>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>Экономия = разница стоимостей × число операций</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Прирост восстановленных поездок, %</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>[ДОПУЩЕНИЕ] доля чувствительных микролокаций</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Дополнительная выручка, тыс. руб.</t>
-        </is>
-      </c>
-      <c r="B21" s="6">
-        <f>ROUND(B4*B20/100*B5/1000,0)</f>
-        <v/>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>0,06 × поездки × чек</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Расходы на стимулы, тыс. руб.</t>
-        </is>
-      </c>
-      <c r="B22" s="6">
-        <f>ROUND(B13*B17/1000,0)</f>
-        <v/>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>Стимул × операции</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>ЧИСТЫЙ ЭФФЕКТ УПС (базовый сценарий), тыс. руб.</t>
-        </is>
-      </c>
-      <c r="B23" s="32">
-        <f>B19+B21-B22</f>
-        <v/>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>§3.2: 4480 + 8140 – 2820 = 9 790</t>
-        </is>
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Затраты S3, млн руб.</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="n">
+        <v>-48</v>
+      </c>
+      <c r="C13" s="38" t="n">
+        <v>-48</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>ЧИСТЫЙ ЭФФЕКТ S3, год 1, млн руб.</t>
+        </is>
+      </c>
+      <c r="B14" s="33">
+        <f>SUM(B9:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="33">
+        <f>SUM(C9:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="33">
+        <f>SUM(D9:D13)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vkr/VKR_findata.xlsx
+++ b/vkr/VKR_findata.xlsx
@@ -1856,7 +1856,7 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>Эффект 2. УПС-пилот Екатеринбург</t>
+          <t>Эффект 2. УПС-пилот Екатеринбург (EBITDA)</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -1871,16 +1871,16 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>Базовый сценарий (замещение 20 % ребалансировки) — см. лист УПС_расчёт</t>
+          <t>Чистая экономия (3,5 млн, прямой EBITDA) + доп. выручка 8,2 млн × маржа 25 % = 2,05 EBITDA</t>
         </is>
       </c>
       <c r="E4" s="20">
-        <f>'УПС_расчёт'!$C$26</f>
+        <f>ROUND('УПС_расчёт'!$C$23 + 'УПС_расчёт'!$C$24*0.25, 0)</f>
         <v/>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>§3.2 ВКР, лист «УПС_расчёт»</t>
+          <t>§3.2 ВКР, лист «УПС_расчёт», пересчёт через EBITDA-маржу 25 %</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>[ДОПУЩЕНИЕ — отраслевая оценка; подлежит калибровке]</t>
+          <t>Данные эксперта А. — стоимость одной операции переноса самоката</t>
         </is>
       </c>
     </row>
@@ -2700,11 +2700,11 @@
         </is>
       </c>
       <c r="B16" s="30" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Тиражирование §3.2 на СПб, Крд, Нск (≈ 4× базы пилота, с учётом разных утилизаций)</t>
+          <t>Коэф. 3,0 млн EBITDA / 1 млн поездок Q2+Q3 × 13 млн сезонных поездок R2-кластера</t>
         </is>
       </c>
     </row>

--- a/vkr/VKR_findata.xlsx
+++ b/vkr/VKR_findata.xlsx
@@ -1831,9 +1831,10 @@
       <c r="C13" s="6" t="n">
         <v>26.5</v>
       </c>
-      <c r="D13" s="16">
-        <f> 15×0,5 + 10×0,3 + 80×0,2 = 26.5</f>
-        <v/>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: 15×0,5 + 10×0,3 + 80×0,2 = 26.5</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1884,9 +1885,10 @@
       <c r="C17" s="6" t="n">
         <v>136426</v>
       </c>
-      <c r="D17" s="16">
-        <f> поездки × чек / 1000 = 1819014 × 75 / 1000 ≈ 136,426</f>
-        <v/>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: поездки × чек / 1000 = 1819014 × 75 / 1000 ≈ 136,426</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1901,9 +1903,10 @@
       <c r="C18" s="6" t="n">
         <v>75034</v>
       </c>
-      <c r="D18" s="16">
-        <f> 136,426 × 55% ≈ 75,034</f>
-        <v/>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: 136,426 × 55% ≈ 75,034</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1918,9 +1921,10 @@
       <c r="C19" s="6" t="n">
         <v>22510</v>
       </c>
-      <c r="D19" s="16">
-        <f> 75,034 × 30% ≈ 22,510</f>
-        <v/>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: 75,034 × 30% ≈ 22,510</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1935,9 +1939,10 @@
       <c r="C20" s="6" t="n">
         <v>187586</v>
       </c>
-      <c r="D20" s="16">
-        <f> 22,510×1000 / 120 ≈ 187,586</f>
-        <v/>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: 22,510×1000 / 120 ≈ 187,586</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1952,9 +1957,10 @@
       <c r="C21" s="6" t="n">
         <v>37517</v>
       </c>
-      <c r="D21" s="16">
-        <f> 187,586 × 20% ≈ 37,517</f>
-        <v/>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: 187,586 × 20% ≈ 37,517</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1969,9 +1975,10 @@
       <c r="C23" s="6" t="n">
         <v>3508</v>
       </c>
-      <c r="D23" s="16">
-        <f> (120–26.5) × 37,517 / 1000 ≈ 3,508</f>
-        <v/>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: (120–26.5) × 37,517 / 1000 ≈ 3,508</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1986,9 +1993,10 @@
       <c r="C24" s="6" t="n">
         <v>8186</v>
       </c>
-      <c r="D24" s="16">
-        <f> 1819014 × 6% × 75 / 1000 ≈ 8,186</f>
-        <v/>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: 1819014 × 6% × 75 / 1000 ≈ 8,186</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -2003,9 +2011,10 @@
       <c r="C26" s="18" t="n">
         <v>11693</v>
       </c>
-      <c r="D26" s="16">
-        <f> 3,508 + 8,186 ≈ 11,693</f>
-        <v/>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: 3,508 + 8,186 ≈ 11,693</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -2020,9 +2029,10 @@
       <c r="C27" s="18" t="n">
         <v>5554</v>
       </c>
-      <c r="D27" s="16">
-        <f> экономия (уже EBITDA) + доп. выручка × 25% маржа = 3,508 + 2,046 ≈ 5,554</f>
-        <v/>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: экономия (уже EBITDA) + доп. выручка × 25% маржа = 3,508 + 2,046 ≈ 5,554</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2194,9 +2204,10 @@
       <c r="E3" s="24" t="n">
         <v>11581</v>
       </c>
-      <c r="F3" s="16">
-        <f> 1544195 × 0,03 × 0,25 = 11,581</f>
-        <v/>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: 1544195 × 0,03 × 0,25 = 11,581</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2223,9 +2234,10 @@
       <c r="E4" s="24" t="n">
         <v>5554</v>
       </c>
-      <c r="F4" s="16">
-        <f> 3508 + 8186 × 0,25 ≈ 5554 тыс. руб.</f>
-        <v/>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: 3508 + 8186 × 0,25 ≈ 5554 тыс. руб.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -2252,9 +2264,10 @@
       <c r="E5" s="24" t="n">
         <v>52528</v>
       </c>
-      <c r="F5" s="16">
-        <f> 2626407 × 0,02 = 52,528</f>
-        <v/>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>расчёт: 2626407 × 0,02 = 52,528</t>
+        </is>
       </c>
     </row>
     <row r="6">

--- a/vkr/VKR_findata.xlsx
+++ b/vkr/VKR_findata.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Эффекты" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводная_финмодель" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Чувствительность" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPV_IRR" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,11 +23,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="+0.0;-0.0;0.0"/>
     <numFmt numFmtId="166" formatCode="0&quot; %&quot;"/>
     <numFmt numFmtId="167" formatCode="+#,##0.0;-#,##0.0;0.0"/>
+    <numFmt numFmtId="168" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -165,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -213,6 +215,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2833,4 +2842,341 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Инвестиционные показатели сценария S3 (NPV, Payback, ROI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>Денежные потоки сценария S3 (млн руб.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>CF, млн руб.</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="21" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Год 0 (запуск, capex)</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="n">
+        <v>-8</v>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Capex на IT-инфраструктуру УПС (геозоны, push-таргетинг, движок стимулов)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="21" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Год 1 (operating)</t>
+        </is>
+      </c>
+      <c r="B6" s="37" t="n">
+        <v>33</v>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Чистый эффект 25 + перенос capex 8 из Y1 в Y0 = 33 млн руб. операционного потока</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="21" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Год 2</t>
+        </is>
+      </c>
+      <c r="B7" s="37" t="n">
+        <v>90</v>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Середина диапазона +80...+100 (тиражирование УПС на 4 R2-города)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="21" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Год 3</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Стабилизация эффекта без новых тиражирований</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="21" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>Расчёт NPV для разных ставок дисконтирования</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>NPV, млн руб.</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="21" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Только для сопоставления (ниже текущей ключевой ставки)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="21" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>20 %</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="n">
+        <v>134.1</v>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Сценарий снижения ключевой ставки ЦБ</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="21" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>БАЗОВЫЙ: ключевая ставка ЦБ 21 % + 1 п.п. риск-премии</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="21" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>25 %</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Консервативный: ключевая ставка + 4 п.п. риск-премии</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="21" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>30 %</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Очень консервативный</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="inlineStr">
+        <is>
+          <t>Другие показатели инвестиционной привлекательности</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Период окупаемости (Payback), мес.</t>
+        </is>
+      </c>
+      <c r="B19" s="38" t="inlineStr">
+        <is>
+          <t>≈ 8</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>48 млн затрат / (73 млн эффекта / 12 мес) ≈ 7,9 мес</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="21" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>ROI год 1</t>
+        </is>
+      </c>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>52 %</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>25 / 48 × 100</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>ROI год 2</t>
+        </is>
+      </c>
+      <c r="B21" s="38" t="inlineStr">
+        <is>
+          <t>243 %</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>90 / 37 × 100</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="21" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>IRR</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> &gt; 100 % (не информативен)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Низкая капитальная интенсивность делает IRR гипертрофированной; для таких проектов корректнее использовать NPV и payback</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="21" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C20:E20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/vkr/VKR_findata.xlsx
+++ b/vkr/VKR_findata.xlsx
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Только для сопоставления (ниже текущей ключевой ставки)</t>
+          <t>Только для сопоставления (мягкий сценарий)</t>
         </is>
       </c>
       <c r="D12" s="20" t="n"/>
@@ -3007,15 +3007,15 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>20 %</t>
+          <t>18 %</t>
         </is>
       </c>
       <c r="B13" s="28" t="n">
-        <v>134.1</v>
+        <v>139.4</v>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Сценарий снижения ключевой ставки ЦБ</t>
+          <t>Снижение ключевой ставки ЦБ ниже сценария</t>
         </is>
       </c>
       <c r="D13" s="20" t="n"/>
@@ -3024,15 +3024,15 @@
     <row r="14">
       <c r="A14" s="38" t="inlineStr">
         <is>
-          <t>22 %</t>
+          <t>20 %</t>
         </is>
       </c>
       <c r="B14" s="39" t="n">
-        <v>129.1</v>
+        <v>134.1</v>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>БАЗОВЫЙ: ключевая ставка ЦБ 21 % + 1 п.п. риск-премии</t>
+          <t>БАЗОВЫЙ: ориентир стоимости капитала цифрового сегмента группы МТС в условиях снижения ключевой ставки к 2026 г.</t>
         </is>
       </c>
       <c r="D14" s="20" t="n"/>
@@ -3041,15 +3041,15 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>25 %</t>
+          <t>23 %</t>
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>122.1</v>
+        <v>126.7</v>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Консервативный: ключевая ставка + 4 п.п. риск-премии</t>
+          <t>Консервативный: +3 п.п. к базовому за счёт риск-премии сегмента</t>
         </is>
       </c>
       <c r="D15" s="20" t="n"/>
@@ -3058,11 +3058,11 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>30 %</t>
+          <t>25 %</t>
         </is>
       </c>
       <c r="B16" s="28" t="n">
-        <v>111.6</v>
+        <v>122.1</v>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
